--- a/diseases/d123/2010-2014.xlsx
+++ b/diseases/d123/2010-2014.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.01864506151518533</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1705,9 +1699,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1853,9 +1844,6 @@
       <c r="O8" t="n">
         <v>5</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.1022670142654304</v>
       </c>
@@ -2397,9 +2385,6 @@
       <c r="O11" t="n">
         <v>3</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.055935184545556</v>
       </c>
@@ -2793,9 +2778,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2941,9 +2923,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3485,9 +3464,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3881,9 +3857,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -4029,9 +4002,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4573,9 +4543,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4969,9 +4936,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -5117,9 +5081,6 @@
       <c r="O26" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.04090680570617215</v>
       </c>
@@ -5661,9 +5622,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -6057,9 +6015,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6205,9 +6160,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6749,9 +6701,6 @@
       <c r="O35" t="n">
         <v>3</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.055935184545556</v>
       </c>
@@ -7145,9 +7094,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7293,9 +7239,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7837,9 +7780,6 @@
       <c r="O41" t="n">
         <v>10</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.1864506151518533</v>
       </c>
@@ -8233,9 +8173,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -8381,9 +8318,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8925,9 +8859,6 @@
       <c r="O47" t="n">
         <v>42</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.7830925836377839</v>
       </c>
@@ -9321,9 +9252,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9469,9 +9397,6 @@
       <c r="O50" t="n">
         <v>3</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.06136020855925821</v>
       </c>
@@ -10013,9 +9938,6 @@
       <c r="O53" t="n">
         <v>23</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.4288364148492626</v>
       </c>
@@ -10409,9 +10331,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -10557,9 +10476,6 @@
       <c r="O56" t="n">
         <v>5</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.1022670142654304</v>
       </c>
@@ -11101,9 +11017,6 @@
       <c r="O59" t="n">
         <v>5</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.09322530757592666</v>
       </c>
@@ -11497,9 +11410,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -11645,9 +11555,6 @@
       <c r="O62" t="n">
         <v>5</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.1022670142654304</v>
       </c>
@@ -12189,9 +12096,6 @@
       <c r="O65" t="n">
         <v>4</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.07458024606074132</v>
       </c>
@@ -12585,9 +12489,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -12733,9 +12634,6 @@
       <c r="O68" t="n">
         <v>9</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.1840806256777746</v>
       </c>
@@ -13277,9 +13175,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -13673,9 +13568,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -13821,9 +13713,6 @@
       <c r="O74" t="n">
         <v>4</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.08181361141234429</v>
       </c>
@@ -14365,9 +14254,6 @@
       <c r="O77" t="n">
         <v>1</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.01855893231204766</v>
       </c>
@@ -14761,9 +14647,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -15157,9 +15040,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -15305,9 +15185,6 @@
       <c r="O82" t="n">
         <v>11</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.2220890585200631</v>
       </c>
@@ -15849,9 +15726,6 @@
       <c r="O85" t="n">
         <v>1</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.01855893231204766</v>
       </c>
@@ -16245,9 +16119,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -16393,9 +16264,6 @@
       <c r="O88" t="n">
         <v>20</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.4037982882182966</v>
       </c>
@@ -16937,9 +16805,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -17333,9 +17198,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -17481,9 +17343,6 @@
       <c r="O94" t="n">
         <v>18</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.3634184593964669</v>
       </c>
@@ -18025,9 +17884,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -18421,9 +18277,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -18569,9 +18422,6 @@
       <c r="O100" t="n">
         <v>8</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.1615193152873186</v>
       </c>
@@ -19113,9 +18963,6 @@
       <c r="O103" t="n">
         <v>2</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.03711786462409532</v>
       </c>
@@ -19509,9 +19356,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -19657,9 +19501,6 @@
       <c r="O106" t="n">
         <v>3</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.06056974323274449</v>
       </c>
@@ -20201,9 +20042,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -20597,9 +20435,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -20745,9 +20580,6 @@
       <c r="O112" t="n">
         <v>3</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.06056974323274449</v>
       </c>
@@ -21437,9 +21269,6 @@
       <c r="O116" t="n">
         <v>6</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.111353593872286</v>
       </c>
@@ -21833,9 +21662,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -21981,9 +21807,6 @@
       <c r="O119" t="n">
         <v>4</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.08075965764365932</v>
       </c>
@@ -22525,9 +22348,6 @@
       <c r="O122" t="n">
         <v>31</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.5753269016734774</v>
       </c>
@@ -22921,9 +22741,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -23069,9 +22886,6 @@
       <c r="O125" t="n">
         <v>19</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.3836083738073818</v>
       </c>
@@ -23613,9 +23427,6 @@
       <c r="O128" t="n">
         <v>20</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.3711786462409532</v>
       </c>
@@ -24009,9 +23820,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -24157,9 +23965,6 @@
       <c r="O131" t="n">
         <v>11</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.2220890585200631</v>
       </c>
@@ -24701,9 +24506,6 @@
       <c r="O134" t="n">
         <v>13</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.2412661200566196</v>
       </c>
@@ -25097,9 +24899,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -25245,9 +25044,6 @@
       <c r="O137" t="n">
         <v>19</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.3836083738073818</v>
       </c>
@@ -25789,9 +25585,6 @@
       <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.01855893231204766</v>
       </c>
@@ -26185,9 +25978,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -26333,9 +26123,6 @@
       <c r="O143" t="n">
         <v>39</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.7874066620256784</v>
       </c>
@@ -26877,9 +26664,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -27273,9 +27057,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -27421,9 +27202,6 @@
       <c r="O149" t="n">
         <v>25</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.5047478602728707</v>
       </c>
@@ -27965,9 +27743,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -28361,9 +28136,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -28757,9 +28529,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -28905,9 +28674,6 @@
       <c r="O157" t="n">
         <v>7</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.1394850907873585</v>
       </c>
@@ -29449,9 +29215,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -29845,9 +29608,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -29993,9 +29753,6 @@
       <c r="O163" t="n">
         <v>11</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.2191908569515633</v>
       </c>
@@ -30537,9 +30294,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -30933,9 +30687,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -31081,9 +30832,6 @@
       <c r="O169" t="n">
         <v>1</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -31625,9 +31373,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -32021,9 +31766,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -32169,9 +31911,6 @@
       <c r="O175" t="n">
         <v>1</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -32713,9 +32452,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -33109,9 +32845,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -33257,9 +32990,6 @@
       <c r="O181" t="n">
         <v>2</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.03985288308210241</v>
       </c>
@@ -33801,9 +33531,6 @@
       <c r="O184" t="n">
         <v>3</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.05541218678376863</v>
       </c>
@@ -34197,9 +33924,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -34345,9 +34069,6 @@
       <c r="O187" t="n">
         <v>3</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.05977932462315363</v>
       </c>
@@ -34889,9 +34610,6 @@
       <c r="O190" t="n">
         <v>7</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.1292951024954601</v>
       </c>
@@ -35285,9 +35003,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -35433,9 +35148,6 @@
       <c r="O193" t="n">
         <v>2</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.03985288308210241</v>
       </c>
@@ -35977,9 +35689,6 @@
       <c r="O196" t="n">
         <v>62</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>1.145185193531218</v>
       </c>
@@ -36373,9 +36082,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -36521,9 +36227,6 @@
       <c r="O199" t="n">
         <v>4</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.07970576616420483</v>
       </c>
@@ -37065,9 +36768,6 @@
       <c r="O202" t="n">
         <v>105</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>1.939426537431902</v>
       </c>
@@ -37461,9 +37161,6 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
@@ -37609,9 +37306,6 @@
       <c r="O205" t="n">
         <v>6</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.1195586492463073</v>
       </c>
@@ -38597,9 +38291,6 @@
       <c r="O211" t="n">
         <v>41</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.7572998860448379</v>
       </c>
@@ -38993,9 +38684,6 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
@@ -39141,9 +38829,6 @@
       <c r="O214" t="n">
         <v>8</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.1594115323284097</v>
       </c>
@@ -40277,9 +39962,6 @@
       <c r="O221" t="n">
         <v>15</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.2770609339188431</v>
       </c>
@@ -40673,9 +40355,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -40821,9 +40500,6 @@
       <c r="O224" t="n">
         <v>3</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.05977932462315363</v>
       </c>
@@ -42105,9 +41781,6 @@
       <c r="O232" t="n">
         <v>2</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.03694145785584575</v>
       </c>
@@ -42501,9 +42174,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -42649,9 +42319,6 @@
       <c r="O235" t="n">
         <v>2</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.03985288308210241</v>
       </c>
@@ -43933,9 +43600,6 @@
       <c r="O243" t="n">
         <v>1</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -44329,9 +43993,6 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -44725,9 +44386,6 @@
       <c r="O247" t="n">
         <v>0</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0</v>
       </c>
@@ -44873,9 +44531,6 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -46157,9 +45812,6 @@
       <c r="O256" t="n">
         <v>1</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -46701,9 +46353,6 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -46849,9 +46498,6 @@
       <c r="O260" t="n">
         <v>0</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0</v>
       </c>
@@ -47985,9 +47631,6 @@
       <c r="O267" t="n">
         <v>0</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0</v>
       </c>
@@ -48529,9 +48172,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
@@ -48677,9 +48317,6 @@
       <c r="O271" t="n">
         <v>1</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -49961,9 +49598,6 @@
       <c r="O279" t="n">
         <v>0</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0</v>
       </c>
@@ -50357,9 +49991,6 @@
       <c r="O281" t="n">
         <v>0</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0</v>
       </c>
@@ -50505,9 +50136,6 @@
       <c r="O282" t="n">
         <v>5</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0.09842278471718557</v>
       </c>
@@ -51789,9 +51417,6 @@
       <c r="O290" t="n">
         <v>1</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -52185,9 +51810,6 @@
       <c r="O292" t="n">
         <v>0</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0</v>
       </c>
@@ -52333,9 +51955,6 @@
       <c r="O293" t="n">
         <v>0</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0</v>
       </c>
@@ -53765,9 +53384,6 @@
       <c r="O302" t="n">
         <v>0</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0</v>
       </c>
@@ -54161,9 +53777,6 @@
       <c r="O304" t="n">
         <v>0</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>0</v>
       </c>
@@ -54309,9 +53922,6 @@
       <c r="O305" t="n">
         <v>2</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0.03936911388687422</v>
       </c>
@@ -55593,9 +55203,6 @@
       <c r="O313" t="n">
         <v>3</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0.0551566605436645</v>
       </c>
@@ -55989,9 +55596,6 @@
       <c r="O315" t="n">
         <v>0</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0</v>
       </c>
@@ -56137,9 +55741,6 @@
       <c r="O316" t="n">
         <v>4</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>0.07873822777374845</v>
       </c>
@@ -57421,9 +57022,6 @@
       <c r="O324" t="n">
         <v>4</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0.07354221405821933</v>
       </c>
@@ -57817,9 +57415,6 @@
       <c r="O326" t="n">
         <v>0</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0</v>
       </c>
@@ -57965,9 +57560,6 @@
       <c r="O327" t="n">
         <v>4</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0.07873822777374845</v>
       </c>
@@ -59397,9 +58989,6 @@
       <c r="O336" t="n">
         <v>4</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>0.07354221405821933</v>
       </c>
@@ -59793,9 +59382,6 @@
       <c r="O338" t="n">
         <v>0</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>0</v>
       </c>
@@ -59941,9 +59527,6 @@
       <c r="O339" t="n">
         <v>4</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0.07873822777374845</v>
       </c>
@@ -61225,9 +60808,6 @@
       <c r="O347" t="n">
         <v>1</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -61621,9 +61201,6 @@
       <c r="O349" t="n">
         <v>0</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0</v>
       </c>
@@ -61769,9 +61346,6 @@
       <c r="O350" t="n">
         <v>4</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>0.07873822777374845</v>
       </c>
@@ -63053,9 +62627,6 @@
       <c r="O358" t="n">
         <v>0</v>
       </c>
-      <c r="Q358" t="n">
-        <v>0</v>
-      </c>
       <c r="R358" t="n">
         <v>0</v>
       </c>
@@ -63597,9 +63168,6 @@
       <c r="O361" t="n">
         <v>0</v>
       </c>
-      <c r="Q361" t="n">
-        <v>0</v>
-      </c>
       <c r="R361" t="n">
         <v>0</v>
       </c>
@@ -63745,9 +63313,6 @@
       <c r="O362" t="n">
         <v>3</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0.05905367083031134</v>
       </c>
@@ -65029,9 +64594,6 @@
       <c r="O370" t="n">
         <v>0</v>
       </c>
-      <c r="Q370" t="n">
-        <v>0</v>
-      </c>
       <c r="R370" t="n">
         <v>0</v>
       </c>
@@ -65425,9 +64987,6 @@
       <c r="O372" t="n">
         <v>0</v>
       </c>
-      <c r="Q372" t="n">
-        <v>0</v>
-      </c>
       <c r="R372" t="n">
         <v>0</v>
       </c>
@@ -65573,9 +65132,6 @@
       <c r="O373" t="n">
         <v>1</v>
       </c>
-      <c r="Q373" t="n">
-        <v>0</v>
-      </c>
       <c r="R373" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -66857,9 +66413,6 @@
       <c r="O381" t="n">
         <v>0</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0</v>
       </c>
@@ -67253,9 +66806,6 @@
       <c r="O383" t="n">
         <v>0</v>
       </c>
-      <c r="Q383" t="n">
-        <v>0</v>
-      </c>
       <c r="R383" t="n">
         <v>0</v>
       </c>
@@ -67649,9 +67199,6 @@
       <c r="O385" t="n">
         <v>0</v>
       </c>
-      <c r="Q385" t="n">
-        <v>0</v>
-      </c>
       <c r="R385" t="n">
         <v>0</v>
       </c>
@@ -67797,9 +67344,6 @@
       <c r="O386" t="n">
         <v>1</v>
       </c>
-      <c r="Q386" t="n">
-        <v>0</v>
-      </c>
       <c r="R386" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -69229,9 +68773,6 @@
       <c r="O395" t="n">
         <v>0</v>
       </c>
-      <c r="Q395" t="n">
-        <v>0</v>
-      </c>
       <c r="R395" t="n">
         <v>0</v>
       </c>
@@ -69625,9 +69166,6 @@
       <c r="O397" t="n">
         <v>0</v>
       </c>
-      <c r="Q397" t="n">
-        <v>0</v>
-      </c>
       <c r="R397" t="n">
         <v>0</v>
       </c>
@@ -69773,9 +69311,6 @@
       <c r="O398" t="n">
         <v>1</v>
       </c>
-      <c r="Q398" t="n">
-        <v>0</v>
-      </c>
       <c r="R398" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -71057,9 +70592,6 @@
       <c r="O406" t="n">
         <v>0</v>
       </c>
-      <c r="Q406" t="n">
-        <v>0</v>
-      </c>
       <c r="R406" t="n">
         <v>0</v>
       </c>
@@ -71453,9 +70985,6 @@
       <c r="O408" t="n">
         <v>0</v>
       </c>
-      <c r="Q408" t="n">
-        <v>0</v>
-      </c>
       <c r="R408" t="n">
         <v>0</v>
       </c>
@@ -71601,9 +71130,6 @@
       <c r="O409" t="n">
         <v>1</v>
       </c>
-      <c r="Q409" t="n">
-        <v>0</v>
-      </c>
       <c r="R409" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -72885,9 +72411,6 @@
       <c r="O417" t="n">
         <v>0</v>
       </c>
-      <c r="Q417" t="n">
-        <v>0</v>
-      </c>
       <c r="R417" t="n">
         <v>0</v>
       </c>
@@ -73281,9 +72804,6 @@
       <c r="O419" t="n">
         <v>0</v>
       </c>
-      <c r="Q419" t="n">
-        <v>0</v>
-      </c>
       <c r="R419" t="n">
         <v>0</v>
       </c>
@@ -73429,9 +72949,6 @@
       <c r="O420" t="n">
         <v>2</v>
       </c>
-      <c r="Q420" t="n">
-        <v>0</v>
-      </c>
       <c r="R420" t="n">
         <v>0.0389302360437537</v>
       </c>
@@ -74713,9 +74230,6 @@
       <c r="O428" t="n">
         <v>1</v>
       </c>
-      <c r="Q428" t="n">
-        <v>0</v>
-      </c>
       <c r="R428" t="n">
         <v>0.01830937124886756</v>
       </c>
@@ -75109,9 +74623,6 @@
       <c r="O430" t="n">
         <v>0</v>
       </c>
-      <c r="Q430" t="n">
-        <v>0</v>
-      </c>
       <c r="R430" t="n">
         <v>0</v>
       </c>
@@ -75257,9 +74768,6 @@
       <c r="O431" t="n">
         <v>0</v>
       </c>
-      <c r="Q431" t="n">
-        <v>0</v>
-      </c>
       <c r="R431" t="n">
         <v>0</v>
       </c>
@@ -76689,9 +76197,6 @@
       <c r="O440" t="n">
         <v>0</v>
       </c>
-      <c r="Q440" t="n">
-        <v>0</v>
-      </c>
       <c r="R440" t="n">
         <v>0</v>
       </c>
@@ -77085,9 +76590,6 @@
       <c r="O442" t="n">
         <v>0</v>
       </c>
-      <c r="Q442" t="n">
-        <v>0</v>
-      </c>
       <c r="R442" t="n">
         <v>0</v>
       </c>
@@ -77233,9 +76735,6 @@
       <c r="O443" t="n">
         <v>0</v>
       </c>
-      <c r="Q443" t="n">
-        <v>0</v>
-      </c>
       <c r="R443" t="n">
         <v>0</v>
       </c>
@@ -78517,9 +78016,6 @@
       <c r="O451" t="n">
         <v>1</v>
       </c>
-      <c r="Q451" t="n">
-        <v>0</v>
-      </c>
       <c r="R451" t="n">
         <v>0.01830937124886756</v>
       </c>
@@ -78913,9 +78409,6 @@
       <c r="O453" t="n">
         <v>0</v>
       </c>
-      <c r="Q453" t="n">
-        <v>0</v>
-      </c>
       <c r="R453" t="n">
         <v>0</v>
       </c>
@@ -79061,9 +78554,6 @@
       <c r="O454" t="n">
         <v>3</v>
       </c>
-      <c r="Q454" t="n">
-        <v>0</v>
-      </c>
       <c r="R454" t="n">
         <v>0.05839535406563053</v>
       </c>
@@ -80345,9 +79835,6 @@
       <c r="O462" t="n">
         <v>1</v>
       </c>
-      <c r="Q462" t="n">
-        <v>0</v>
-      </c>
       <c r="R462" t="n">
         <v>0.01830937124886756</v>
       </c>
@@ -80889,9 +80376,6 @@
       <c r="O465" t="n">
         <v>0</v>
       </c>
-      <c r="Q465" t="n">
-        <v>0</v>
-      </c>
       <c r="R465" t="n">
         <v>0</v>
       </c>
@@ -81037,9 +80521,6 @@
       <c r="O466" t="n">
         <v>1</v>
       </c>
-      <c r="Q466" t="n">
-        <v>0</v>
-      </c>
       <c r="R466" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -82321,9 +81802,6 @@
       <c r="O474" t="n">
         <v>5</v>
       </c>
-      <c r="Q474" t="n">
-        <v>0</v>
-      </c>
       <c r="R474" t="n">
         <v>0.09154685624433782</v>
       </c>
@@ -82717,9 +82195,6 @@
       <c r="O476" t="n">
         <v>0</v>
       </c>
-      <c r="Q476" t="n">
-        <v>0</v>
-      </c>
       <c r="R476" t="n">
         <v>0</v>
       </c>
@@ -82865,9 +82340,6 @@
       <c r="O477" t="n">
         <v>12</v>
       </c>
-      <c r="Q477" t="n">
-        <v>0</v>
-      </c>
       <c r="R477" t="n">
         <v>0.2335814162625221</v>
       </c>
@@ -84149,9 +83621,6 @@
       <c r="O485" t="n">
         <v>2</v>
       </c>
-      <c r="Q485" t="n">
-        <v>0</v>
-      </c>
       <c r="R485" t="n">
         <v>0.03661874249773513</v>
       </c>
@@ -84545,9 +84014,6 @@
       <c r="O487" t="n">
         <v>0</v>
       </c>
-      <c r="Q487" t="n">
-        <v>0</v>
-      </c>
       <c r="R487" t="n">
         <v>0</v>
       </c>
@@ -84693,9 +84159,6 @@
       <c r="O488" t="n">
         <v>11</v>
       </c>
-      <c r="Q488" t="n">
-        <v>0</v>
-      </c>
       <c r="R488" t="n">
         <v>0.2141162982406453</v>
       </c>
@@ -86125,9 +85588,6 @@
       <c r="O497" t="n">
         <v>0</v>
       </c>
-      <c r="Q497" t="n">
-        <v>0</v>
-      </c>
       <c r="R497" t="n">
         <v>0</v>
       </c>
@@ -86521,9 +85981,6 @@
       <c r="O499" t="n">
         <v>0</v>
       </c>
-      <c r="Q499" t="n">
-        <v>0</v>
-      </c>
       <c r="R499" t="n">
         <v>0</v>
       </c>
@@ -86669,9 +86126,6 @@
       <c r="O500" t="n">
         <v>12</v>
       </c>
-      <c r="Q500" t="n">
-        <v>0</v>
-      </c>
       <c r="R500" t="n">
         <v>0.2335814162625221</v>
       </c>
@@ -87953,9 +87407,6 @@
       <c r="O508" t="n">
         <v>0</v>
       </c>
-      <c r="Q508" t="n">
-        <v>0</v>
-      </c>
       <c r="R508" t="n">
         <v>0</v>
       </c>
@@ -88349,9 +87800,6 @@
       <c r="O510" t="n">
         <v>0</v>
       </c>
-      <c r="Q510" t="n">
-        <v>0</v>
-      </c>
       <c r="R510" t="n">
         <v>0</v>
       </c>
@@ -88496,9 +87944,6 @@
       </c>
       <c r="O511" t="n">
         <v>2</v>
-      </c>
-      <c r="Q511" t="n">
-        <v>0</v>
       </c>
       <c r="R511" t="n">
         <v>0.0389302360437537</v>
